--- a/test_data/test-data.xlsx
+++ b/test_data/test-data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\risk-desktop\app\test_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\risk-desktop\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA9F3BC-3AE4-4D28-8C7A-9A7E4548ABD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2B9B18-EDC3-423B-8159-393F3A71A967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI_TestData" sheetId="1" r:id="rId1"/>
@@ -491,15 +491,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.08203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.9140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -510,7 +510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -521,7 +521,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -529,28 +529,6 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -565,9 +543,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -587,7 +565,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -607,7 +585,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -637,10 +615,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -663,7 +641,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -684,6 +662,28 @@
       </c>
       <c r="G2" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
